--- a/Testing-reportHW04_6810301028.xlsx
+++ b/Testing-reportHW04_6810301028.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my-homework_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8B8EA29B-22E5-427B-8AFD-B4791E457531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BE5173C4-87BC-473F-B2DE-1E156ED542D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
     <author>Sarayut Chaisuriya</author>
   </authors>
   <commentList>
-    <comment ref="I6" authorId="0" shapeId="6145" xr:uid="{00000000-0006-0000-0500-000001000000}">
+    <comment ref="I6" authorId="0" shapeId="5121" xr:uid="{00000000-0006-0000-0500-000001000000}">
       <text>
         <r>
           <rPr>
@@ -408,7 +408,7 @@
     <author>Sarayut Chaisuriya</author>
   </authors>
   <commentList>
-    <comment ref="I6" authorId="0" shapeId="5121" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="I6" authorId="0" shapeId="6145" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -588,7 +588,7 @@
     <author>Sarayut Chaisuriya</author>
   </authors>
   <commentList>
-    <comment ref="I6" authorId="0" shapeId="9218" xr:uid="{FC25C79D-C874-49AD-88CD-4AD89DE2D9B8}">
+    <comment ref="I6" authorId="0" shapeId="8193" xr:uid="{FC25C79D-C874-49AD-88CD-4AD89DE2D9B8}">
       <text>
         <r>
           <rPr>
@@ -683,7 +683,7 @@
     <author>Sarayut Chaisuriya</author>
   </authors>
   <commentList>
-    <comment ref="I6" authorId="0" shapeId="8193" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="I6" authorId="0" shapeId="9217" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
           <rPr>
@@ -773,7 +773,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="496" uniqueCount="164">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="498" uniqueCount="164">
   <si>
     <t>Test Report</t>
   </si>
@@ -1736,37 +1736,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1779,22 +1787,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1817,45 +1854,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1942,7 +1942,7 @@
             <xdr:cNvPr id="2049" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31C4A1F4-3B65-49B9-A5FA-B249F8E687A0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F3F2C61-ECD0-4E17-AF1B-C444BB85868F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2055,7 +2055,7 @@
             <xdr:cNvPr id="2050" name="Comment 2" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE044342-D945-4676-B726-43C835989070}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03E9A2EB-D779-4A66-AB99-10DF4950054B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2173,7 +2173,7 @@
             <xdr:cNvPr id="3073" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DD5203D-7B1E-4C45-8AFE-F57F1DA8537D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59C4C62B-FBDE-40EA-A416-DF548F6E7238}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2378,7 +2378,7 @@
             <xdr:cNvPr id="4097" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74992EED-38DD-4D9B-A91A-8D860E01BAAB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68644429-539A-42C5-9748-0E7E1B184C6D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2580,10 +2580,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6145" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="5121" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAE75B24-21F3-423B-8F2E-7DACA32A16D3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8406CD3A-79C2-4925-B836-6ECE4CC18A39}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2785,10 +2785,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5121" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="6145" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE436D22-DCEE-4B18-AFF9-3CB2ACCB8436}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DAAD8E7-BACB-45FA-8038-971CEB95F1BA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2993,7 +2993,7 @@
             <xdr:cNvPr id="7169" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86043466-A892-4C5F-A9E4-8DD5C7E5F624}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA293F45-59F9-4716-B428-68A8802878B4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3172,10 +3172,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9218" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="8193" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9825E6A-87F4-4F5D-88F0-D3D1366F7736}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E8548E1-D20A-433D-958C-856CE7D08280}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3393,10 +3393,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8193" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="9217" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{104C6750-B4C8-439D-87C3-E4AF69FE3AC4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{962B9768-6B49-499B-A637-567CC8DC14DA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3868,17 +3868,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="109" t="s">
+      <c r="J1" s="65" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3889,20 +3889,20 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="67"/>
+      <c r="D2" s="77"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67" t="s">
+      <c r="G2" s="77"/>
+      <c r="H2" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3920,10 +3920,10 @@
         <v>10</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="68"/>
+      <c r="I3" s="78"/>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3944,10 +3944,10 @@
         <v>14</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="65" t="s">
+      <c r="H4" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="65"/>
+      <c r="I4" s="75"/>
       <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3970,42 +3970,42 @@
       <c r="G5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="69"/>
+      <c r="I5" s="73"/>
       <c r="J5" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70" t="s">
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70" t="s">
+      <c r="G6" s="74"/>
+      <c r="H6" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
       <c r="F7" s="17" t="s">
         <v>27</v>
       </c>
@@ -4026,12 +4026,12 @@
       <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="71" t="str">
+      <c r="B8" s="69" t="str">
         <f>'TC01'!B6</f>
         <v>Load_Data_Range_CSV</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
       <c r="E8" s="19" t="s">
         <v>33</v>
       </c>
@@ -4045,12 +4045,12 @@
       <c r="A9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="72" t="str">
+      <c r="B9" s="70" t="str">
         <f>'TC02'!B6</f>
         <v>Invalid_Range_Validation</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
       <c r="E9" s="19" t="s">
         <v>33</v>
       </c>
@@ -4064,12 +4064,12 @@
       <c r="A10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="72" t="str">
+      <c r="B10" s="70" t="str">
         <f>'TC03'!B6</f>
         <v>Data_Filtering_Exe</v>
       </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
       <c r="E10" s="19" t="s">
         <v>33</v>
       </c>
@@ -4083,12 +4083,12 @@
       <c r="A11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="72" t="str">
+      <c r="B11" s="70" t="str">
         <f>'TC04'!B6</f>
         <v>Read_As_Text_UI_Test</v>
       </c>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
       <c r="E11" s="19" t="s">
         <v>33</v>
       </c>
@@ -4102,11 +4102,11 @@
       <c r="A12" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
       <c r="E12" s="28" t="s">
         <v>33</v>
       </c>
@@ -4120,10 +4120,14 @@
       <c r="A13" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="28"/>
+      <c r="B13" s="72" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="28" t="s">
+        <v>33</v>
+      </c>
       <c r="F13" s="24"/>
       <c r="G13" s="5"/>
       <c r="H13" s="25"/>
@@ -4132,9 +4136,9 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
       <c r="E14" s="28"/>
       <c r="F14" s="24"/>
       <c r="G14" s="5"/>
@@ -4144,9 +4148,9 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
       <c r="E15" s="28"/>
       <c r="F15" s="24"/>
       <c r="G15" s="5"/>
@@ -4156,9 +4160,9 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
       <c r="E16" s="28"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -4168,9 +4172,9 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
-      <c r="B17" s="74"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
       <c r="E17" s="28"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -4180,9 +4184,9 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="28"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
       <c r="E18" s="28"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -4192,9 +4196,9 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="28"/>
-      <c r="B19" s="74"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
       <c r="E19" s="28"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -4204,9 +4208,9 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
-      <c r="B20" s="74"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
       <c r="E20" s="28"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -4216,9 +4220,9 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
       <c r="E21" s="29"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -4230,10 +4234,10 @@
       <c r="A22" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="76"/>
+      <c r="C22" s="67"/>
       <c r="G22" s="34" t="s">
         <v>40</v>
       </c>
@@ -4250,85 +4254,89 @@
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
+      <c r="J24" s="66"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="75"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="75"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="75"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="75"/>
-      <c r="C27" s="75"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="75"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="66"/>
     </row>
     <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="75"/>
-      <c r="C28" s="75"/>
-      <c r="D28" s="75"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
       <c r="F28" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="75"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:J6"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
@@ -4343,18 +4351,14 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4380,21 +4384,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="80"/>
+      <c r="C2" s="84"/>
       <c r="D2" s="34" t="s">
         <v>44</v>
       </c>
@@ -4406,8 +4410,8 @@
       <c r="A3" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
       <c r="D3" s="34" t="s">
         <v>45</v>
       </c>
@@ -4419,10 +4423,10 @@
       <c r="A4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="70" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="72"/>
+      <c r="C4" s="70"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
@@ -4448,10 +4452,10 @@
       <c r="B6" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="78" t="s">
+      <c r="C6" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="78"/>
+      <c r="D6" s="82"/>
       <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4459,10 +4463,10 @@
       <c r="B7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="82" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="78"/>
+      <c r="D7" s="82"/>
       <c r="E7" s="42"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4470,8 +4474,8 @@
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
       <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4479,8 +4483,8 @@
       <c r="B9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
       <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4515,14 +4519,14 @@
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -4532,10 +4536,10 @@
       <c r="B15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="78" t="s">
+      <c r="C15" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="78"/>
+      <c r="D15" s="82"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -4543,8 +4547,8 @@
       <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -4552,8 +4556,8 @@
       <c r="B17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -4561,8 +4565,8 @@
       <c r="B18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -4597,33 +4601,33 @@
       <c r="B22" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
       <c r="E22" s="42"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
       <c r="B25" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="82" t="s">
+      <c r="C25" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="82"/>
+      <c r="D25" s="80"/>
       <c r="E25" s="48" t="s">
         <v>31</v>
       </c>
@@ -4632,22 +4636,22 @@
       <c r="A26" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="74" t="s">
+      <c r="C26" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="74"/>
+      <c r="D26" s="72"/>
       <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
       <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="49"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="74"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
       <c r="E28" s="42"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -4658,54 +4662,54 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="49"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
       <c r="E30" s="42"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
       <c r="E31" s="42"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
       <c r="E32" s="42"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="74"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
       <c r="E33" s="42"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
       <c r="E34" s="42"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="82" t="s">
+      <c r="C36" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="82"/>
+      <c r="D36" s="80"/>
       <c r="E36" s="48" t="s">
         <v>31</v>
       </c>
@@ -4715,29 +4719,29 @@
         <v>63</v>
       </c>
       <c r="B37" s="42"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
       <c r="E37" s="42"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="49"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="84"/>
-      <c r="D38" s="84"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="79"/>
       <c r="E38" s="42"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="49"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="84"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
       <c r="E39" s="42"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="49"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="84"/>
-      <c r="D40" s="84"/>
+      <c r="C40" s="79"/>
+      <c r="D40" s="79"/>
       <c r="E40" s="42"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -4745,31 +4749,44 @@
         <v>64</v>
       </c>
       <c r="B41" s="42"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="79"/>
       <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
       <c r="E42" s="42"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="84"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="79"/>
       <c r="E43" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
@@ -4782,24 +4799,11 @@
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
   </mergeCells>
   <pageMargins left="0.75000000000000011" right="0.75000000000000011" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -4830,14 +4834,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
         <v>148</v>
@@ -4850,19 +4854,19 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="77"/>
+      <c r="E2" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4879,10 +4883,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="68"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4902,10 +4906,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="65"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4927,27 +4931,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="69"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="86" t="s">
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="86"/>
+      <c r="H6" s="89"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -4956,117 +4960,117 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70" t="s">
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70" t="s">
+      <c r="F12" s="74"/>
+      <c r="G12" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70" t="s">
+      <c r="H12" s="74"/>
+      <c r="I12" s="74" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="70"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
       <c r="G13" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="70"/>
+      <c r="I13" s="74"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="44">
         <v>1</v>
       </c>
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="87"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87" t="s">
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="87"/>
+      <c r="F14" s="86"/>
       <c r="G14" t="s">
         <v>146</v>
       </c>
@@ -5077,15 +5081,15 @@
       <c r="A15" s="44">
         <v>2</v>
       </c>
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="87"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="87" t="s">
+      <c r="C15" s="86"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="87"/>
+      <c r="F15" s="86"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
@@ -5096,15 +5100,15 @@
       <c r="A16" s="44">
         <v>3</v>
       </c>
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87" t="s">
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="87"/>
+      <c r="F16" s="86"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -5115,15 +5119,15 @@
       <c r="A17" s="44">
         <v>4</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87" t="s">
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="87"/>
+      <c r="F17" s="86"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -5132,22 +5136,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="87"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -5178,26 +5182,26 @@
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
       <c r="E22" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
@@ -5212,29 +5216,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:I13"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -5247,6 +5228,29 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.19000000000000003" top="0.27" bottom="0.16000000000000003" header="0.27" footer="0.16000000000000003"/>
   <pageSetup paperSize="0" scale="90" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -5277,16 +5281,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="65" t="s">
         <v>148</v>
       </c>
     </row>
@@ -5297,19 +5301,19 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="E2" s="89" t="s">
+      <c r="D2" s="103"/>
+      <c r="E2" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="90"/>
-      <c r="G2" s="89" t="s">
+      <c r="F2" s="103"/>
+      <c r="G2" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="91"/>
-      <c r="I2" s="90"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="103"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -5326,10 +5330,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="92"/>
+      <c r="H3" s="105"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5349,10 +5353,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="93"/>
+      <c r="H4" s="106"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5374,27 +5378,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="94"/>
+      <c r="H5" s="107"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="85" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="95" t="s">
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="95"/>
+      <c r="H6" s="108"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -5403,127 +5407,127 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="66" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="99"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="98" t="s">
+      <c r="C13" s="95"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="100"/>
-      <c r="G13" s="104" t="s">
+      <c r="F13" s="96"/>
+      <c r="G13" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="105"/>
-      <c r="I13" s="96" t="s">
+      <c r="H13" s="101"/>
+      <c r="I13" s="92" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="97"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="103"/>
+      <c r="A14" s="93"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="99"/>
       <c r="G14" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="97"/>
+      <c r="I14" s="93"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="106" t="s">
+      <c r="B15" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="81"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="106" t="s">
+      <c r="C15" s="85"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="90" t="s">
         <v>106</v>
       </c>
-      <c r="F15" s="78"/>
+      <c r="F15" s="82"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
@@ -5534,15 +5538,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="106" t="s">
+      <c r="B16" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="106" t="s">
+      <c r="C16" s="85"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="90" t="s">
         <v>147</v>
       </c>
-      <c r="F16" s="78"/>
+      <c r="F16" s="82"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -5553,15 +5557,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="106" t="s">
+      <c r="B17" s="90" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="106"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106" t="s">
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="106"/>
+      <c r="F17" s="90"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -5572,15 +5576,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="106" t="s">
+      <c r="B18" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="106" t="s">
+      <c r="C18" s="85"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="90" t="s">
         <v>110</v>
       </c>
-      <c r="F18" s="78"/>
+      <c r="F18" s="82"/>
       <c r="G18" t="s">
         <v>146</v>
       </c>
@@ -5589,11 +5593,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="107"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="83"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="81"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -5624,46 +5628,46 @@
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
       <c r="E22" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -5678,30 +5682,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="B9:I9"/>
@@ -5716,6 +5696,30 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -5748,16 +5752,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="65" t="s">
         <v>148</v>
       </c>
     </row>
@@ -5768,19 +5772,19 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="77"/>
+      <c r="E2" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -5797,10 +5801,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="68"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5820,10 +5824,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="65"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5845,27 +5849,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="69"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="86" t="s">
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="86"/>
+      <c r="H6" s="89"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -5874,127 +5878,127 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="85" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="85" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70" t="s">
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70" t="s">
+      <c r="F13" s="74"/>
+      <c r="G13" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70" t="s">
+      <c r="H13" s="74"/>
+      <c r="I13" s="74" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="70"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
       <c r="G14" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="70"/>
+      <c r="I14" s="74"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108" t="s">
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109" t="s">
         <v>125</v>
       </c>
-      <c r="F15" s="108"/>
+      <c r="F15" s="109"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
@@ -6005,15 +6009,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="108" t="s">
+      <c r="B16" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108" t="s">
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="108"/>
+      <c r="F16" s="109"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -6024,15 +6028,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="108" t="s">
+      <c r="B17" s="109" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="108"/>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108" t="s">
+      <c r="C17" s="109"/>
+      <c r="D17" s="109"/>
+      <c r="E17" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="108"/>
+      <c r="F17" s="109"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -6043,15 +6047,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="109" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="108"/>
-      <c r="D18" s="108"/>
-      <c r="E18" s="108" t="s">
+      <c r="C18" s="109"/>
+      <c r="D18" s="109"/>
+      <c r="E18" s="109" t="s">
         <v>131</v>
       </c>
-      <c r="F18" s="108"/>
+      <c r="F18" s="109"/>
       <c r="G18" t="s">
         <v>146</v>
       </c>
@@ -6084,46 +6088,46 @@
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
       <c r="E21" t="s">
         <v>83</v>
       </c>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="75"/>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
     </row>
     <row r="25" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
@@ -6138,30 +6142,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -6174,6 +6154,30 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -6205,16 +6209,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="1"/>
-      <c r="J1" s="109" t="s">
+      <c r="J1" s="65" t="s">
         <v>148</v>
       </c>
     </row>
@@ -6225,19 +6229,19 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="77"/>
+      <c r="E2" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -6256,10 +6260,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="68"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6279,10 +6283,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="65"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6304,27 +6308,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="69"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="85" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="86" t="s">
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="86"/>
+      <c r="H6" s="89"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -6333,127 +6337,127 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="85" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="85" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70" t="s">
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70" t="s">
+      <c r="F13" s="74"/>
+      <c r="G13" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70" t="s">
+      <c r="H13" s="74"/>
+      <c r="I13" s="74" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="70"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
       <c r="G14" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="70"/>
+      <c r="I14" s="74"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="109" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108" t="s">
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109" t="s">
         <v>117</v>
       </c>
-      <c r="F15" s="108"/>
+      <c r="F15" s="109"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
@@ -6464,15 +6468,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="108" t="s">
+      <c r="B16" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108" t="s">
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="109" t="s">
         <v>119</v>
       </c>
-      <c r="F16" s="108"/>
+      <c r="F16" s="109"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -6483,15 +6487,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="79" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84" t="s">
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="84"/>
+      <c r="F17" s="79"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -6500,22 +6504,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="84"/>
-      <c r="C19" s="84"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -6546,46 +6550,46 @@
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
       <c r="E22" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -6600,32 +6604,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -6638,6 +6616,32 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -6670,16 +6674,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="1"/>
-      <c r="J1" s="109" t="s">
+      <c r="J1" s="65" t="s">
         <v>148</v>
       </c>
     </row>
@@ -6690,19 +6694,19 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="77"/>
+      <c r="E2" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -6719,10 +6723,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="68"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6742,10 +6746,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="65"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6767,27 +6771,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="69"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="85" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="86" t="s">
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="86"/>
+      <c r="H6" s="89"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -6796,127 +6800,127 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="85" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="85" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="85" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70" t="s">
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70" t="s">
+      <c r="F13" s="74"/>
+      <c r="G13" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70" t="s">
+      <c r="H13" s="74"/>
+      <c r="I13" s="74" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="70"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
       <c r="G14" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="70"/>
+      <c r="I14" s="74"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="109" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108" t="s">
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="108"/>
+      <c r="F15" s="109"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
@@ -6927,15 +6931,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="108" t="s">
+      <c r="B16" s="109" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108" t="s">
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="109" t="s">
         <v>138</v>
       </c>
-      <c r="F16" s="108"/>
+      <c r="F16" s="109"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -6946,15 +6950,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84" t="s">
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="F17" s="84"/>
+      <c r="F17" s="79"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -6965,15 +6969,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="79" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84" t="s">
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="F18" s="84"/>
+      <c r="F18" s="79"/>
       <c r="G18" t="s">
         <v>146</v>
       </c>
@@ -6982,11 +6986,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="84"/>
-      <c r="C19" s="84"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -7017,46 +7021,46 @@
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
       <c r="E22" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -7071,6 +7075,32 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B24:D24"/>
@@ -7083,32 +7113,6 @@
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
@@ -7140,16 +7144,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="1"/>
-      <c r="J1" s="109" t="s">
+      <c r="J1" s="65" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7160,19 +7164,19 @@
       <c r="B2" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="77"/>
+      <c r="E2" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
@@ -7191,10 +7195,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="68"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -7214,10 +7218,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="65"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7239,27 +7243,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="69"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="86" t="s">
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="86"/>
+      <c r="H6" s="89"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -7268,171 +7272,171 @@
       <c r="A7" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="64"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="64"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="64"/>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="85" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="85"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70" t="s">
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70" t="s">
+      <c r="F17" s="74"/>
+      <c r="G17" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70" t="s">
+      <c r="H17" s="74"/>
+      <c r="I17" s="74" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="70"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
       <c r="G18" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="70"/>
+      <c r="I18" s="74"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1</v>
       </c>
-      <c r="B19" s="84" t="s">
+      <c r="B19" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="84"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84" t="s">
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="F19" s="84"/>
+      <c r="F19" s="79"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -7441,28 +7445,28 @@
       <c r="A20" s="4">
         <v>2</v>
       </c>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="79" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84" t="s">
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="F20" s="84"/>
+      <c r="F20" s="79"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="84"/>
-      <c r="C21" s="84"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84" t="s">
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="84"/>
+      <c r="F21" s="79"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
@@ -7471,15 +7475,15 @@
       <c r="A22" s="4">
         <v>3</v>
       </c>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="79" t="s">
         <v>158</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84" t="s">
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="79" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="84"/>
+      <c r="F22" s="79"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
@@ -7488,15 +7492,15 @@
       <c r="A23" s="4">
         <v>4</v>
       </c>
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="84"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84" t="s">
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79" t="s">
         <v>161</v>
       </c>
-      <c r="F23" s="84"/>
+      <c r="F23" s="79"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
@@ -7505,114 +7509,114 @@
       <c r="A24" s="4">
         <v>5</v>
       </c>
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84" t="s">
+      <c r="C24" s="79"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="F24" s="84"/>
+      <c r="F24" s="79"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="84"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="84"/>
-      <c r="C27" s="84"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="84"/>
+      <c r="B27" s="79"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="79"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="84"/>
-      <c r="C28" s="84"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="84"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="84"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="84"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="79"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="84"/>
-      <c r="C31" s="84"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="79"/>
+      <c r="F31" s="79"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="79"/>
+      <c r="F32" s="79"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="84"/>
-      <c r="C33" s="84"/>
-      <c r="D33" s="84"/>
-      <c r="E33" s="84"/>
-      <c r="F33" s="84"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
@@ -7643,46 +7647,46 @@
       <c r="A36" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
       <c r="E36" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="68"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="64"/>
-      <c r="B37" s="75"/>
-      <c r="C37" s="75"/>
-      <c r="D37" s="75"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="66"/>
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="66"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="64"/>
-      <c r="B38" s="75"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="64"/>
-      <c r="B39" s="75"/>
-      <c r="C39" s="75"/>
-      <c r="D39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="66"/>
     </row>
     <row r="40" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58" t="s">
@@ -7697,26 +7701,31 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="E31:F31"/>
@@ -7733,32 +7742,27 @@
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
     <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{4C4DB9CF-C79C-4E5A-A850-965613BF762B}"/>
@@ -7790,14 +7794,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
         <v>1</v>
@@ -7810,19 +7814,19 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="77"/>
+      <c r="E2" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -7841,10 +7845,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="68"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -7862,10 +7866,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="65"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -7887,25 +7891,25 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="69"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="86" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="86"/>
+      <c r="H6" s="89"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -7914,328 +7918,328 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="75"/>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="85" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="85"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70" t="s">
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70" t="s">
+      <c r="F17" s="74"/>
+      <c r="G17" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70" t="s">
+      <c r="H17" s="74"/>
+      <c r="I17" s="74" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="70"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
       <c r="G18" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="70"/>
+      <c r="I18" s="74"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44">
         <v>1</v>
       </c>
-      <c r="B19" s="84"/>
-      <c r="C19" s="84"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="84"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="84"/>
-      <c r="C21" s="84"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="84"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="79"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="79"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="84"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="79"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
-      <c r="B24" s="84"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
+      <c r="B24" s="79"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="79"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="84"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="84"/>
-      <c r="C27" s="84"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="84"/>
+      <c r="B27" s="79"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="79"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="84"/>
-      <c r="C28" s="84"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="84"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="84"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="84"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="79"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="84"/>
-      <c r="C31" s="84"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="79"/>
+      <c r="F31" s="79"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="79"/>
+      <c r="F32" s="79"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="84"/>
-      <c r="C33" s="84"/>
-      <c r="D33" s="84"/>
-      <c r="E33" s="84"/>
-      <c r="F33" s="84"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="44"/>
-      <c r="B34" s="84"/>
-      <c r="C34" s="84"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="84"/>
-      <c r="F34" s="84"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="44"/>
@@ -8266,46 +8270,46 @@
       <c r="A37" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="68"/>
       <c r="E37" t="s">
         <v>83</v>
       </c>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="68"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
-      <c r="B38" s="75"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="75"/>
-      <c r="C39" s="75"/>
-      <c r="D39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="66"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="75"/>
-      <c r="C40" s="75"/>
-      <c r="D40" s="75"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="66"/>
     </row>
     <row r="41" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
@@ -8320,52 +8324,12 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="B6:F6"/>
@@ -8378,12 +8342,52 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>

--- a/Testing-reportHW04_6810301028.xlsx
+++ b/Testing-reportHW04_6810301028.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my-homework_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F5E16687-9905-4F33-80C8-80F7E6C805E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0B15B92D-16CA-4158-A5A3-89D8307BC1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -986,53 +986,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1040,67 +1046,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1655,15 +1655,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
       <c r="I1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -1676,20 +1676,20 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="78"/>
+      <c r="D2" s="69"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78" t="s">
+      <c r="G2" s="69"/>
+      <c r="H2" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1709,10 +1709,10 @@
         <v>7</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="79"/>
+      <c r="I3" s="70"/>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1733,10 +1733,10 @@
         <v>10</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="76"/>
+      <c r="I4" s="67"/>
       <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1759,42 +1759,42 @@
       <c r="G5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="74" t="s">
+      <c r="H5" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="74"/>
+      <c r="I5" s="71"/>
       <c r="J5" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75" t="s">
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75" t="s">
+      <c r="G6" s="72"/>
+      <c r="H6" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="75"/>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
       <c r="F7" s="17" t="s">
         <v>23</v>
       </c>
@@ -1815,12 +1815,12 @@
       <c r="A8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="70" t="str">
+      <c r="B8" s="73" t="str">
         <f>'TC01'!B6</f>
         <v>Load_Data_Range_CSV</v>
       </c>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
       <c r="E8" s="19" t="s">
         <v>29</v>
       </c>
@@ -1834,12 +1834,12 @@
       <c r="A9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="71" t="str">
+      <c r="B9" s="74" t="str">
         <f>'TC02'!B6</f>
         <v>Invalid_Range_Validation</v>
       </c>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
       <c r="E9" s="19" t="s">
         <v>29</v>
       </c>
@@ -1853,12 +1853,12 @@
       <c r="A10" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="71" t="str">
+      <c r="B10" s="74" t="str">
         <f>'TC03'!B6</f>
         <v>Data_Filtering_Exe</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
       <c r="E10" s="19" t="s">
         <v>29</v>
       </c>
@@ -1872,12 +1872,12 @@
       <c r="A11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="71" t="str">
+      <c r="B11" s="74" t="str">
         <f>'TC04'!B6</f>
         <v>Read_As_Text_UI_Test</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
       <c r="E11" s="19" t="s">
         <v>29</v>
       </c>
@@ -1891,11 +1891,11 @@
       <c r="A12" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="76" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
       <c r="E12" s="28" t="s">
         <v>29</v>
       </c>
@@ -1909,11 +1909,11 @@
       <c r="A13" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
       <c r="E13" s="28" t="s">
         <v>29</v>
       </c>
@@ -1925,9 +1925,9 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
       <c r="E14" s="28"/>
       <c r="F14" s="24"/>
       <c r="G14" s="5"/>
@@ -1937,9 +1937,9 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
       <c r="E15" s="28"/>
       <c r="F15" s="24"/>
       <c r="G15" s="5"/>
@@ -1949,9 +1949,9 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="76"/>
       <c r="E16" s="28"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -1961,9 +1961,9 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
       <c r="E17" s="28"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1973,9 +1973,9 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="28"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
       <c r="E18" s="28"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -1985,9 +1985,9 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="28"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
       <c r="E19" s="28"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -1997,9 +1997,9 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
       <c r="E20" s="28"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -2009,9 +2009,9 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
       <c r="E21" s="29"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -2023,10 +2023,10 @@
       <c r="A22" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="68"/>
+      <c r="C22" s="78"/>
       <c r="G22" s="34" t="s">
         <v>36</v>
       </c>
@@ -2043,89 +2043,85 @@
       <c r="A23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="77"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="67"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="77"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="77"/>
     </row>
     <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
       <c r="F28" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
@@ -2140,14 +2136,18 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2173,21 +2173,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="85"/>
+      <c r="C2" s="82"/>
       <c r="D2" s="34" t="s">
         <v>40</v>
       </c>
@@ -2199,8 +2199,8 @@
       <c r="A3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
       <c r="D3" s="34" t="s">
         <v>41</v>
       </c>
@@ -2212,10 +2212,10 @@
       <c r="A4" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="71"/>
+      <c r="C4" s="74"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
@@ -2241,8 +2241,8 @@
       <c r="B6" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
       <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2250,10 +2250,10 @@
       <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="83"/>
+      <c r="D7" s="80"/>
       <c r="E7" s="42"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2261,8 +2261,8 @@
       <c r="B8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2270,8 +2270,8 @@
       <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
       <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2306,14 +2306,14 @@
       <c r="B13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2323,8 +2323,8 @@
       <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2332,8 +2332,8 @@
       <c r="B16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2341,8 +2341,8 @@
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2350,8 +2350,8 @@
       <c r="B18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2386,33 +2386,33 @@
       <c r="B22" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
       <c r="E22" s="42"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
       <c r="B25" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="81"/>
+      <c r="D25" s="84"/>
       <c r="E25" s="48" t="s">
         <v>27</v>
       </c>
@@ -2421,22 +2421,22 @@
       <c r="A26" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="73" t="s">
+      <c r="C26" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="D26" s="73"/>
+      <c r="D26" s="76"/>
       <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
       <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="49"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
       <c r="E28" s="42"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2447,54 +2447,54 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="49"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
       <c r="E30" s="42"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
       <c r="E31" s="42"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
       <c r="E32" s="42"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
       <c r="E33" s="42"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
       <c r="E34" s="42"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="75"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="81" t="s">
+      <c r="C36" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="81"/>
+      <c r="D36" s="84"/>
       <c r="E36" s="48" t="s">
         <v>27</v>
       </c>
@@ -2504,29 +2504,29 @@
         <v>57</v>
       </c>
       <c r="B37" s="42"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="80"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="86"/>
       <c r="E37" s="42"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="49"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
+      <c r="C38" s="86"/>
+      <c r="D38" s="86"/>
       <c r="E38" s="42"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="49"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="86"/>
       <c r="E39" s="42"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="49"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="86"/>
       <c r="E40" s="42"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2534,32 +2534,43 @@
         <v>58</v>
       </c>
       <c r="B41" s="42"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
       <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="86"/>
       <c r="E42" s="42"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="86"/>
       <c r="E43" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
@@ -2572,23 +2583,12 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.75000000000000011" right="0.75000000000000011" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -2613,14 +2613,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
         <v>141</v>
@@ -2633,19 +2633,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -2664,10 +2664,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -2687,10 +2687,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2712,144 +2712,144 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75" t="s">
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75" t="s">
+      <c r="F12" s="72"/>
+      <c r="G12" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75" t="s">
+      <c r="H12" s="72"/>
+      <c r="I12" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="75"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
       <c r="G13" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="75"/>
+      <c r="I13" s="72"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="44">
         <v>1</v>
       </c>
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="87"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87" t="s">
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="F14" s="87"/>
+      <c r="F14" s="89"/>
       <c r="G14" t="s">
         <v>139</v>
       </c>
@@ -2860,15 +2860,15 @@
       <c r="A15" s="44">
         <v>2</v>
       </c>
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="89" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="87"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="87" t="s">
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="87"/>
+      <c r="F15" s="89"/>
       <c r="G15" t="s">
         <v>139</v>
       </c>
@@ -2879,15 +2879,15 @@
       <c r="A16" s="44">
         <v>3</v>
       </c>
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87" t="s">
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="87"/>
+      <c r="F16" s="89"/>
       <c r="G16" t="s">
         <v>139</v>
       </c>
@@ -2898,15 +2898,15 @@
       <c r="A17" s="44">
         <v>4</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87" t="s">
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="87"/>
+      <c r="F17" s="89"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -2915,22 +2915,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="87"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -2961,26 +2961,26 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
@@ -2995,6 +2995,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:I13"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -3007,29 +3030,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.19000000000000003" top="0.27" bottom="0.16000000000000003" header="0.27" footer="0.16000000000000003"/>
   <pageSetup paperSize="0" scale="90" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -3054,14 +3054,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -3074,19 +3074,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="104"/>
-      <c r="E2" s="103" t="s">
+      <c r="D2" s="92"/>
+      <c r="E2" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="103" t="s">
+      <c r="F2" s="92"/>
+      <c r="G2" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="105"/>
-      <c r="I2" s="104"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="92"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3105,10 +3105,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="106"/>
+      <c r="H3" s="94"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -3128,10 +3128,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="107"/>
+      <c r="H4" s="95"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -3153,154 +3153,154 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="108"/>
+      <c r="H5" s="96"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="109" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="109"/>
+      <c r="H6" s="97"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="95" t="s">
+      <c r="C13" s="101"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="97"/>
-      <c r="G13" s="101" t="s">
+      <c r="F13" s="102"/>
+      <c r="G13" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="102"/>
-      <c r="I13" s="93" t="s">
+      <c r="H13" s="107"/>
+      <c r="I13" s="98" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="94"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="100"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="105"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="94"/>
+      <c r="I14" s="99"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="108" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="91" t="s">
+      <c r="C15" s="83"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="108" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="83"/>
+      <c r="F15" s="80"/>
       <c r="G15" t="s">
         <v>139</v>
       </c>
@@ -3311,15 +3311,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="91" t="s">
+      <c r="B16" s="108" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="91" t="s">
+      <c r="C16" s="83"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="83"/>
+      <c r="F16" s="80"/>
       <c r="G16" t="s">
         <v>139</v>
       </c>
@@ -3330,15 +3330,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="108" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91" t="s">
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="91"/>
+      <c r="F17" s="108"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -3349,15 +3349,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="91" t="s">
+      <c r="B18" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="91" t="s">
+      <c r="C18" s="83"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="83"/>
+      <c r="F18" s="80"/>
       <c r="G18" t="s">
         <v>139</v>
       </c>
@@ -3366,11 +3366,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="82"/>
+      <c r="B19" s="109"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -3401,46 +3401,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -3455,6 +3455,30 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="B9:I9"/>
@@ -3469,30 +3493,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -3520,14 +3520,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -3540,19 +3540,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3571,10 +3571,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3594,10 +3594,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3619,140 +3619,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75" t="s">
+      <c r="F13" s="72"/>
+      <c r="G13" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="72"/>
+      <c r="I13" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="75"/>
+      <c r="I14" s="72"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -3796,15 +3796,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80" t="s">
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="80"/>
+      <c r="F17" s="86"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -3813,22 +3813,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -3859,46 +3859,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -3913,6 +3913,32 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -3925,32 +3951,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -3978,14 +3978,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -3998,19 +3998,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4029,10 +4029,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4052,10 +4052,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4077,140 +4077,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75" t="s">
+      <c r="F13" s="72"/>
+      <c r="G13" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="72"/>
+      <c r="I13" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="75"/>
+      <c r="I14" s="72"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -4314,46 +4314,46 @@
       <c r="A21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
       <c r="E21" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
@@ -4368,6 +4368,30 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -4380,30 +4404,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -4430,14 +4430,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -4450,19 +4450,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4481,10 +4481,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4504,10 +4504,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4529,140 +4529,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75" t="s">
+      <c r="F13" s="72"/>
+      <c r="G13" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="72"/>
+      <c r="I13" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="75"/>
+      <c r="I14" s="72"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -4706,15 +4706,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="86" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80" t="s">
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="F17" s="80"/>
+      <c r="F17" s="86"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -4725,15 +4725,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80" t="s">
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86" t="s">
         <v>134</v>
       </c>
-      <c r="F18" s="80"/>
+      <c r="F18" s="86"/>
       <c r="G18" t="s">
         <v>139</v>
       </c>
@@ -4742,11 +4742,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -4777,46 +4777,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -4831,32 +4831,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B24:D24"/>
@@ -4869,6 +4843,32 @@
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
@@ -4895,14 +4895,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -4915,19 +4915,19 @@
       <c r="B2" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
@@ -4946,10 +4946,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4969,10 +4969,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4994,198 +4994,198 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="77" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="64"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="64"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="64"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="75" t="s">
+      <c r="A17" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75" t="s">
+      <c r="F17" s="72"/>
+      <c r="G17" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75" t="s">
+      <c r="H17" s="72"/>
+      <c r="I17" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
       <c r="G18" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="75"/>
+      <c r="I18" s="72"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="86" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80" t="s">
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="F19" s="80"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -5194,28 +5194,28 @@
       <c r="A20" s="4">
         <v>2</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="86" t="s">
         <v>148</v>
       </c>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80" t="s">
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="80"/>
+      <c r="F20" s="86"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80" t="s">
+      <c r="B21" s="86"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86" t="s">
         <v>150</v>
       </c>
-      <c r="F21" s="80"/>
+      <c r="F21" s="86"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
@@ -5224,15 +5224,15 @@
       <c r="A22" s="4">
         <v>3</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="86" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80" t="s">
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86" t="s">
         <v>152</v>
       </c>
-      <c r="F22" s="80"/>
+      <c r="F22" s="86"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
@@ -5241,15 +5241,15 @@
       <c r="A23" s="4">
         <v>4</v>
       </c>
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="86" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80" t="s">
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="F23" s="80"/>
+      <c r="F23" s="86"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
@@ -5258,114 +5258,114 @@
       <c r="A24" s="4">
         <v>5</v>
       </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80" t="s">
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="80"/>
+      <c r="F24" s="86"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="80"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="80"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
@@ -5396,46 +5396,46 @@
       <c r="A36" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
       <c r="E36" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="64"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67"/>
-      <c r="D37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="67"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="64"/>
-      <c r="B38" s="67"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="64"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
     </row>
     <row r="40" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58" t="s">
@@ -5450,16 +5450,42 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="B24:D24"/>
@@ -5476,42 +5502,16 @@
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{4C4DB9CF-C79C-4E5A-A850-965613BF762B}"/>
@@ -5537,14 +5537,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -5557,19 +5557,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -5586,10 +5586,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5607,10 +5607,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5632,353 +5632,353 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="90" t="s">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="75" t="s">
+      <c r="A17" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75" t="s">
+      <c r="F17" s="72"/>
+      <c r="G17" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75" t="s">
+      <c r="H17" s="72"/>
+      <c r="I17" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
       <c r="G18" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="75"/>
+      <c r="I18" s="72"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44">
         <v>1</v>
       </c>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
+      <c r="B21" s="86"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="86"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="86"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="86"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="80"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="80"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="44"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="80"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="86"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="44"/>
@@ -6009,46 +6009,46 @@
       <c r="A37" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
       <c r="E37" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="79"/>
+      <c r="I37" s="79"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
-      <c r="B38" s="67"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
     </row>
     <row r="41" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
@@ -6063,12 +6063,52 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="B6:F6"/>
@@ -6081,52 +6121,12 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>

--- a/Testing-reportHW04_6810301028.xlsx
+++ b/Testing-reportHW04_6810301028.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my-homework_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0B15B92D-16CA-4158-A5A3-89D8307BC1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{400C7078-821C-4EA2-AD4E-37D01A188311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -986,37 +986,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1029,22 +1034,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1067,40 +1101,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1655,15 +1655,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
       <c r="I1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -1676,20 +1676,20 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="69"/>
+      <c r="D2" s="78"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="69" t="s">
+      <c r="F2" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69" t="s">
+      <c r="G2" s="78"/>
+      <c r="H2" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1709,10 +1709,10 @@
         <v>7</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="70" t="s">
+      <c r="H3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="70"/>
+      <c r="I3" s="79"/>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1733,10 +1733,10 @@
         <v>10</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="67"/>
+      <c r="I4" s="76"/>
       <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1759,42 +1759,42 @@
       <c r="G5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="71" t="s">
+      <c r="H5" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="71"/>
+      <c r="I5" s="74"/>
       <c r="J5" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72" t="s">
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="F6" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72" t="s">
+      <c r="G6" s="75"/>
+      <c r="H6" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
       <c r="F7" s="17" t="s">
         <v>23</v>
       </c>
@@ -1815,12 +1815,12 @@
       <c r="A8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="73" t="str">
+      <c r="B8" s="70" t="str">
         <f>'TC01'!B6</f>
         <v>Load_Data_Range_CSV</v>
       </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
       <c r="E8" s="19" t="s">
         <v>29</v>
       </c>
@@ -1834,12 +1834,12 @@
       <c r="A9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="74" t="str">
+      <c r="B9" s="71" t="str">
         <f>'TC02'!B6</f>
         <v>Invalid_Range_Validation</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
       <c r="E9" s="19" t="s">
         <v>29</v>
       </c>
@@ -1853,12 +1853,12 @@
       <c r="A10" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="74" t="str">
+      <c r="B10" s="71" t="str">
         <f>'TC03'!B6</f>
         <v>Data_Filtering_Exe</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
       <c r="E10" s="19" t="s">
         <v>29</v>
       </c>
@@ -1872,12 +1872,12 @@
       <c r="A11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="74" t="str">
+      <c r="B11" s="71" t="str">
         <f>'TC04'!B6</f>
         <v>Read_As_Text_UI_Test</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
       <c r="E11" s="19" t="s">
         <v>29</v>
       </c>
@@ -1891,11 +1891,11 @@
       <c r="A12" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
       <c r="E12" s="28" t="s">
         <v>29</v>
       </c>
@@ -1909,11 +1909,11 @@
       <c r="A13" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="73" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
       <c r="E13" s="28" t="s">
         <v>29</v>
       </c>
@@ -1925,9 +1925,9 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
       <c r="E14" s="28"/>
       <c r="F14" s="24"/>
       <c r="G14" s="5"/>
@@ -1937,9 +1937,9 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="76"/>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
       <c r="E15" s="28"/>
       <c r="F15" s="24"/>
       <c r="G15" s="5"/>
@@ -1949,9 +1949,9 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="76"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
       <c r="E16" s="28"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -1961,9 +1961,9 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
       <c r="E17" s="28"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1973,9 +1973,9 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="28"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
       <c r="E18" s="28"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -1985,9 +1985,9 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="28"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
       <c r="E19" s="28"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -1997,9 +1997,9 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
-      <c r="B20" s="76"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
       <c r="E20" s="28"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -2009,9 +2009,9 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
-      <c r="B21" s="75"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="75"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
       <c r="E21" s="29"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -2023,10 +2023,10 @@
       <c r="A22" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="78"/>
+      <c r="C22" s="68"/>
       <c r="G22" s="34" t="s">
         <v>36</v>
       </c>
@@ -2043,85 +2043,89 @@
       <c r="A23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="79"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="69"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="77"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="77"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="77"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="77"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="67"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
     </row>
     <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
       <c r="F28" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="77"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:J6"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
@@ -2136,18 +2140,14 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2173,21 +2173,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="85" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="82"/>
+      <c r="C2" s="85"/>
       <c r="D2" s="34" t="s">
         <v>40</v>
       </c>
@@ -2199,8 +2199,8 @@
       <c r="A3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
       <c r="D3" s="34" t="s">
         <v>41</v>
       </c>
@@ -2212,10 +2212,10 @@
       <c r="A4" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="74"/>
+      <c r="C4" s="71"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
@@ -2241,8 +2241,8 @@
       <c r="B6" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
       <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2250,10 +2250,10 @@
       <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="83" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="80"/>
+      <c r="D7" s="83"/>
       <c r="E7" s="42"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2261,8 +2261,8 @@
       <c r="B8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
       <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2270,8 +2270,8 @@
       <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
       <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2306,14 +2306,14 @@
       <c r="B13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2323,8 +2323,8 @@
       <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2332,8 +2332,8 @@
       <c r="B16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2341,8 +2341,8 @@
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="82"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2350,8 +2350,8 @@
       <c r="B18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2386,33 +2386,33 @@
       <c r="B22" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
       <c r="E22" s="42"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
       <c r="B25" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="84" t="s">
+      <c r="C25" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="84"/>
+      <c r="D25" s="81"/>
       <c r="E25" s="48" t="s">
         <v>27</v>
       </c>
@@ -2421,22 +2421,22 @@
       <c r="A26" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="D26" s="76"/>
+      <c r="D26" s="73"/>
       <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
       <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="49"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
       <c r="E28" s="42"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2447,54 +2447,54 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="49"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="76"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
       <c r="E30" s="42"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
       <c r="E31" s="42"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
       <c r="E32" s="42"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="76"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
       <c r="E33" s="42"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="76"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
       <c r="E34" s="42"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="84" t="s">
+      <c r="C36" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="84"/>
+      <c r="D36" s="81"/>
       <c r="E36" s="48" t="s">
         <v>27</v>
       </c>
@@ -2504,29 +2504,29 @@
         <v>57</v>
       </c>
       <c r="B37" s="42"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="86"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="80"/>
       <c r="E37" s="42"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="49"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="86"/>
-      <c r="D38" s="86"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
       <c r="E38" s="42"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="49"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="86"/>
-      <c r="D39" s="86"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
       <c r="E39" s="42"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="49"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
       <c r="E40" s="42"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2534,31 +2534,44 @@
         <v>58</v>
       </c>
       <c r="B41" s="42"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
       <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="86"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
       <c r="E42" s="42"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="86"/>
+      <c r="C43" s="80"/>
+      <c r="D43" s="80"/>
       <c r="E43" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
@@ -2571,24 +2584,11 @@
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
   </mergeCells>
   <pageMargins left="0.75000000000000011" right="0.75000000000000011" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -2613,14 +2613,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
         <v>141</v>
@@ -2633,19 +2633,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -2664,10 +2664,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="70"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -2687,10 +2687,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="67"/>
+      <c r="H4" s="76"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2712,144 +2712,144 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="71"/>
+      <c r="H5" s="74"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="86" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="88" t="s">
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="88"/>
+      <c r="H6" s="90"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="82" t="s">
+      <c r="B7" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72" t="s">
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72" t="s">
+      <c r="F12" s="75"/>
+      <c r="G12" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72" t="s">
+      <c r="H12" s="75"/>
+      <c r="I12" s="75" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
+      <c r="A13" s="75"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
       <c r="G13" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="72"/>
+      <c r="I13" s="75"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="44">
         <v>1</v>
       </c>
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89" t="s">
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="F14" s="89"/>
+      <c r="F14" s="87"/>
       <c r="G14" t="s">
         <v>139</v>
       </c>
@@ -2860,15 +2860,15 @@
       <c r="A15" s="44">
         <v>2</v>
       </c>
-      <c r="B15" s="89" t="s">
+      <c r="B15" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89" t="s">
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="89"/>
+      <c r="F15" s="87"/>
       <c r="G15" t="s">
         <v>139</v>
       </c>
@@ -2879,15 +2879,15 @@
       <c r="A16" s="44">
         <v>3</v>
       </c>
-      <c r="B16" s="89" t="s">
+      <c r="B16" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89" t="s">
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="89"/>
+      <c r="F16" s="87"/>
       <c r="G16" t="s">
         <v>139</v>
       </c>
@@ -2898,15 +2898,15 @@
       <c r="A17" s="44">
         <v>4</v>
       </c>
-      <c r="B17" s="89" t="s">
+      <c r="B17" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89" t="s">
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="89"/>
+      <c r="F17" s="87"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -2915,22 +2915,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -2961,26 +2961,26 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="79"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
@@ -2995,29 +2995,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:I13"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -3030,6 +3007,29 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.19000000000000003" top="0.27" bottom="0.16000000000000003" header="0.27" footer="0.16000000000000003"/>
   <pageSetup paperSize="0" scale="90" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -3054,14 +3054,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -3074,19 +3074,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="92"/>
-      <c r="E2" s="91" t="s">
+      <c r="D2" s="104"/>
+      <c r="E2" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="92"/>
-      <c r="G2" s="91" t="s">
+      <c r="F2" s="104"/>
+      <c r="G2" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="93"/>
-      <c r="I2" s="92"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="104"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3105,10 +3105,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="94"/>
+      <c r="H3" s="106"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -3128,10 +3128,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="95"/>
+      <c r="H4" s="107"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -3153,154 +3153,154 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="96"/>
+      <c r="H5" s="108"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="97" t="s">
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="97"/>
+      <c r="H6" s="109"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="86" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="98" t="s">
+      <c r="A13" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="100" t="s">
+      <c r="B13" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="101"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="100" t="s">
+      <c r="C13" s="96"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="102"/>
-      <c r="G13" s="106" t="s">
+      <c r="F13" s="97"/>
+      <c r="G13" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="107"/>
-      <c r="I13" s="98" t="s">
+      <c r="H13" s="102"/>
+      <c r="I13" s="93" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="99"/>
-      <c r="B14" s="103"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="105"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="100"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="99"/>
+      <c r="I14" s="94"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="83"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="108" t="s">
+      <c r="C15" s="86"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="80"/>
+      <c r="F15" s="83"/>
       <c r="G15" t="s">
         <v>139</v>
       </c>
@@ -3311,15 +3311,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="108" t="s">
+      <c r="B16" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="108" t="s">
+      <c r="C16" s="86"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="91" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="80"/>
+      <c r="F16" s="83"/>
       <c r="G16" t="s">
         <v>139</v>
       </c>
@@ -3330,15 +3330,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="108" t="s">
+      <c r="B17" s="91" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="108"/>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108" t="s">
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="108"/>
+      <c r="F17" s="91"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -3349,15 +3349,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="108" t="s">
+      <c r="C18" s="86"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="80"/>
+      <c r="F18" s="83"/>
       <c r="G18" t="s">
         <v>139</v>
       </c>
@@ -3366,11 +3366,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="109"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="85"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="82"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -3401,46 +3401,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="79"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -3455,30 +3455,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="B9:I9"/>
@@ -3493,6 +3469,30 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -3520,14 +3520,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -3540,19 +3540,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3571,10 +3571,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="70"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3594,10 +3594,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="67"/>
+      <c r="H4" s="76"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3619,140 +3619,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="71"/>
+      <c r="H5" s="74"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="86" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="88" t="s">
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="88"/>
+      <c r="H6" s="90"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="86" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72" t="s">
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72" t="s">
+      <c r="F13" s="75"/>
+      <c r="G13" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72" t="s">
+      <c r="H13" s="75"/>
+      <c r="I13" s="75" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="72"/>
+      <c r="I14" s="75"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -3796,15 +3796,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86" t="s">
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="86"/>
+      <c r="F17" s="80"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -3813,22 +3813,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
+      <c r="B18" s="80"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -3859,46 +3859,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="79"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -3913,32 +3913,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -3951,6 +3925,32 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -3978,14 +3978,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -3998,19 +3998,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4029,10 +4029,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="70"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4052,10 +4052,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="67"/>
+      <c r="H4" s="76"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4077,140 +4077,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="71"/>
+      <c r="H5" s="74"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="86" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="88" t="s">
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="88"/>
+      <c r="H6" s="90"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="86" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72" t="s">
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72" t="s">
+      <c r="F13" s="75"/>
+      <c r="G13" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72" t="s">
+      <c r="H13" s="75"/>
+      <c r="I13" s="75" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="72"/>
+      <c r="I14" s="75"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -4314,46 +4314,46 @@
       <c r="A21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
       <c r="E21" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
     </row>
     <row r="25" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
@@ -4368,30 +4368,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -4404,6 +4380,30 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -4430,14 +4430,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -4450,19 +4450,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4481,10 +4481,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="70"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4504,10 +4504,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="67"/>
+      <c r="H4" s="76"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4529,140 +4529,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="71"/>
+      <c r="H5" s="74"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="88" t="s">
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="88"/>
+      <c r="H6" s="90"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="86" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="86" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72" t="s">
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72" t="s">
+      <c r="F13" s="75"/>
+      <c r="G13" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72" t="s">
+      <c r="H13" s="75"/>
+      <c r="I13" s="75" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="72"/>
+      <c r="I14" s="75"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -4706,15 +4706,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86" t="s">
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="F17" s="86"/>
+      <c r="F17" s="80"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -4725,15 +4725,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86" t="s">
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="F18" s="86"/>
+      <c r="F18" s="80"/>
       <c r="G18" t="s">
         <v>139</v>
       </c>
@@ -4742,11 +4742,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -4777,46 +4777,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="79"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -4831,6 +4831,32 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B24:D24"/>
@@ -4843,32 +4869,6 @@
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
@@ -4895,14 +4895,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -4915,19 +4915,19 @@
       <c r="B2" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
@@ -4946,10 +4946,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="70"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4969,10 +4969,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="67"/>
+      <c r="H4" s="76"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4994,198 +4994,198 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="71"/>
+      <c r="H5" s="74"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="88" t="s">
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="88"/>
+      <c r="H6" s="90"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="64"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="64"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="64"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="72" t="s">
+      <c r="B17" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72" t="s">
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72" t="s">
+      <c r="F17" s="75"/>
+      <c r="G17" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72" t="s">
+      <c r="H17" s="75"/>
+      <c r="I17" s="75" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="72"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
       <c r="G18" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="72"/>
+      <c r="I18" s="75"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1</v>
       </c>
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86" t="s">
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="F19" s="86"/>
+      <c r="F19" s="80"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -5194,28 +5194,28 @@
       <c r="A20" s="4">
         <v>2</v>
       </c>
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="80" t="s">
         <v>148</v>
       </c>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86" t="s">
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="86"/>
+      <c r="F20" s="80"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86" t="s">
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80" t="s">
         <v>150</v>
       </c>
-      <c r="F21" s="86"/>
+      <c r="F21" s="80"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
@@ -5224,15 +5224,15 @@
       <c r="A22" s="4">
         <v>3</v>
       </c>
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86" t="s">
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="F22" s="86"/>
+      <c r="F22" s="80"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
@@ -5241,15 +5241,15 @@
       <c r="A23" s="4">
         <v>4</v>
       </c>
-      <c r="B23" s="86" t="s">
+      <c r="B23" s="80" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86" t="s">
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="F23" s="86"/>
+      <c r="F23" s="80"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
@@ -5258,114 +5258,114 @@
       <c r="A24" s="4">
         <v>5</v>
       </c>
-      <c r="B24" s="86" t="s">
+      <c r="B24" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86" t="s">
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="86"/>
+      <c r="F24" s="80"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
+      <c r="B27" s="80"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
+      <c r="B28" s="80"/>
+      <c r="C28" s="80"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
@@ -5396,46 +5396,46 @@
       <c r="A36" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="79"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
       <c r="E36" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
-      <c r="I36" s="79"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="64"/>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="67"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="64"/>
-      <c r="B38" s="77"/>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="67"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="64"/>
-      <c r="B39" s="77"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
     </row>
     <row r="40" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58" t="s">
@@ -5450,6 +5450,52 @@
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="B39:D39"/>
@@ -5466,52 +5512,6 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="F37:I37"/>
     <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{4C4DB9CF-C79C-4E5A-A850-965613BF762B}"/>
@@ -5537,14 +5537,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -5557,19 +5557,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -5586,10 +5586,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="70"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5607,10 +5607,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="67"/>
+      <c r="H4" s="76"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5632,353 +5632,353 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="71"/>
+      <c r="H5" s="74"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="88" t="s">
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="88"/>
+      <c r="H6" s="90"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="86" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="72" t="s">
+      <c r="B17" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72" t="s">
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72" t="s">
+      <c r="F17" s="75"/>
+      <c r="G17" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72" t="s">
+      <c r="H17" s="75"/>
+      <c r="I17" s="75" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="72"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
       <c r="G18" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="72"/>
+      <c r="I18" s="75"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44">
         <v>1</v>
       </c>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="86"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="86"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="86"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
+      <c r="B27" s="80"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
+      <c r="B28" s="80"/>
+      <c r="C28" s="80"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="44"/>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="86"/>
+      <c r="B34" s="80"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="44"/>
@@ -6009,46 +6009,46 @@
       <c r="A37" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
       <c r="E37" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="79"/>
-      <c r="I37" s="79"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
-      <c r="B38" s="77"/>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="67"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="77"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="77"/>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
     </row>
     <row r="41" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
@@ -6063,52 +6063,12 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="B6:F6"/>
@@ -6121,12 +6081,52 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>

--- a/Testing-reportHW04_6810301028.xlsx
+++ b/Testing-reportHW04_6810301028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my-homework_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{400C7078-821C-4EA2-AD4E-37D01A188311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{374CFF98-3B19-43BB-B38C-1F432F0B1234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -986,53 +986,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1040,67 +1046,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1655,15 +1655,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
       <c r="I1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -1676,20 +1676,20 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="78"/>
+      <c r="D2" s="69"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78" t="s">
+      <c r="G2" s="69"/>
+      <c r="H2" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1709,10 +1709,10 @@
         <v>7</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="79"/>
+      <c r="I3" s="70"/>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1733,10 +1733,10 @@
         <v>10</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="76"/>
+      <c r="I4" s="67"/>
       <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1759,42 +1759,42 @@
       <c r="G5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="74" t="s">
+      <c r="H5" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="74"/>
+      <c r="I5" s="71"/>
       <c r="J5" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75" t="s">
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75" t="s">
+      <c r="G6" s="72"/>
+      <c r="H6" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="75"/>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
       <c r="F7" s="17" t="s">
         <v>23</v>
       </c>
@@ -1815,12 +1815,12 @@
       <c r="A8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="70" t="str">
+      <c r="B8" s="73" t="str">
         <f>'TC01'!B6</f>
         <v>Load_Data_Range_CSV</v>
       </c>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
       <c r="E8" s="19" t="s">
         <v>29</v>
       </c>
@@ -1834,12 +1834,12 @@
       <c r="A9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="71" t="str">
+      <c r="B9" s="74" t="str">
         <f>'TC02'!B6</f>
         <v>Invalid_Range_Validation</v>
       </c>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
       <c r="E9" s="19" t="s">
         <v>29</v>
       </c>
@@ -1853,12 +1853,12 @@
       <c r="A10" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="71" t="str">
+      <c r="B10" s="74" t="str">
         <f>'TC03'!B6</f>
         <v>Data_Filtering_Exe</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
       <c r="E10" s="19" t="s">
         <v>29</v>
       </c>
@@ -1872,12 +1872,12 @@
       <c r="A11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="71" t="str">
+      <c r="B11" s="74" t="str">
         <f>'TC04'!B6</f>
         <v>Read_As_Text_UI_Test</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
       <c r="E11" s="19" t="s">
         <v>29</v>
       </c>
@@ -1891,11 +1891,11 @@
       <c r="A12" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="76" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
       <c r="E12" s="28" t="s">
         <v>29</v>
       </c>
@@ -1909,11 +1909,11 @@
       <c r="A13" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
       <c r="E13" s="28" t="s">
         <v>29</v>
       </c>
@@ -1925,9 +1925,9 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
       <c r="E14" s="28"/>
       <c r="F14" s="24"/>
       <c r="G14" s="5"/>
@@ -1937,9 +1937,9 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
       <c r="E15" s="28"/>
       <c r="F15" s="24"/>
       <c r="G15" s="5"/>
@@ -1949,9 +1949,9 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="76"/>
       <c r="E16" s="28"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -1961,9 +1961,9 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
       <c r="E17" s="28"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1973,9 +1973,9 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="28"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
       <c r="E18" s="28"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -1985,9 +1985,9 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="28"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
       <c r="E19" s="28"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -1997,9 +1997,9 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
       <c r="E20" s="28"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -2009,9 +2009,9 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
       <c r="E21" s="29"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -2023,10 +2023,10 @@
       <c r="A22" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="68"/>
+      <c r="C22" s="78"/>
       <c r="G22" s="34" t="s">
         <v>36</v>
       </c>
@@ -2043,89 +2043,85 @@
       <c r="A23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="77"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="67"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="77"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="77"/>
     </row>
     <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
       <c r="F28" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
@@ -2140,14 +2136,18 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2173,21 +2173,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="85"/>
+      <c r="C2" s="82"/>
       <c r="D2" s="34" t="s">
         <v>40</v>
       </c>
@@ -2199,8 +2199,8 @@
       <c r="A3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
       <c r="D3" s="34" t="s">
         <v>41</v>
       </c>
@@ -2212,10 +2212,10 @@
       <c r="A4" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="71"/>
+      <c r="C4" s="74"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
@@ -2241,8 +2241,8 @@
       <c r="B6" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
       <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2250,10 +2250,10 @@
       <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="83"/>
+      <c r="D7" s="80"/>
       <c r="E7" s="42"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2261,8 +2261,8 @@
       <c r="B8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2270,8 +2270,8 @@
       <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
       <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2306,14 +2306,14 @@
       <c r="B13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2323,8 +2323,8 @@
       <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2332,8 +2332,8 @@
       <c r="B16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2341,8 +2341,8 @@
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2350,8 +2350,8 @@
       <c r="B18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2386,33 +2386,33 @@
       <c r="B22" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
       <c r="E22" s="42"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
       <c r="B25" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="81"/>
+      <c r="D25" s="84"/>
       <c r="E25" s="48" t="s">
         <v>27</v>
       </c>
@@ -2421,22 +2421,22 @@
       <c r="A26" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="73" t="s">
+      <c r="C26" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="D26" s="73"/>
+      <c r="D26" s="76"/>
       <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
       <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="49"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
       <c r="E28" s="42"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2447,54 +2447,54 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="49"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
       <c r="E30" s="42"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
       <c r="E31" s="42"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
       <c r="E32" s="42"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
       <c r="E33" s="42"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
       <c r="E34" s="42"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="75"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="81" t="s">
+      <c r="C36" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="81"/>
+      <c r="D36" s="84"/>
       <c r="E36" s="48" t="s">
         <v>27</v>
       </c>
@@ -2504,29 +2504,29 @@
         <v>57</v>
       </c>
       <c r="B37" s="42"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="80"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="86"/>
       <c r="E37" s="42"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="49"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
+      <c r="C38" s="86"/>
+      <c r="D38" s="86"/>
       <c r="E38" s="42"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="49"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="86"/>
       <c r="E39" s="42"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="49"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="86"/>
       <c r="E40" s="42"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2534,32 +2534,43 @@
         <v>58</v>
       </c>
       <c r="B41" s="42"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
       <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="86"/>
       <c r="E42" s="42"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="86"/>
       <c r="E43" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
@@ -2572,23 +2583,12 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.75000000000000011" right="0.75000000000000011" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -2613,14 +2613,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
         <v>141</v>
@@ -2633,19 +2633,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -2664,10 +2664,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -2687,10 +2687,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2712,144 +2712,144 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75" t="s">
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75" t="s">
+      <c r="F12" s="72"/>
+      <c r="G12" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75" t="s">
+      <c r="H12" s="72"/>
+      <c r="I12" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="75"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
       <c r="G13" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="75"/>
+      <c r="I13" s="72"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="44">
         <v>1</v>
       </c>
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="87"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87" t="s">
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="F14" s="87"/>
+      <c r="F14" s="89"/>
       <c r="G14" t="s">
         <v>139</v>
       </c>
@@ -2860,15 +2860,15 @@
       <c r="A15" s="44">
         <v>2</v>
       </c>
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="89" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="87"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="87" t="s">
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="87"/>
+      <c r="F15" s="89"/>
       <c r="G15" t="s">
         <v>139</v>
       </c>
@@ -2879,15 +2879,15 @@
       <c r="A16" s="44">
         <v>3</v>
       </c>
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87" t="s">
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="87"/>
+      <c r="F16" s="89"/>
       <c r="G16" t="s">
         <v>139</v>
       </c>
@@ -2898,15 +2898,15 @@
       <c r="A17" s="44">
         <v>4</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87" t="s">
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="87"/>
+      <c r="F17" s="89"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -2915,22 +2915,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="87"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -2961,26 +2961,26 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
@@ -2995,6 +2995,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:I13"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -3007,29 +3030,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.19000000000000003" top="0.27" bottom="0.16000000000000003" header="0.27" footer="0.16000000000000003"/>
   <pageSetup paperSize="0" scale="90" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -3054,14 +3054,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -3074,19 +3074,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="104"/>
-      <c r="E2" s="103" t="s">
+      <c r="D2" s="92"/>
+      <c r="E2" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="103" t="s">
+      <c r="F2" s="92"/>
+      <c r="G2" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="105"/>
-      <c r="I2" s="104"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="92"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3105,10 +3105,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="106"/>
+      <c r="H3" s="94"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -3128,10 +3128,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="107"/>
+      <c r="H4" s="95"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -3153,154 +3153,154 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="108"/>
+      <c r="H5" s="96"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="109" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="109"/>
+      <c r="H6" s="97"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="95" t="s">
+      <c r="C13" s="101"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="97"/>
-      <c r="G13" s="101" t="s">
+      <c r="F13" s="102"/>
+      <c r="G13" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="102"/>
-      <c r="I13" s="93" t="s">
+      <c r="H13" s="107"/>
+      <c r="I13" s="98" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="94"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="100"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="105"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="94"/>
+      <c r="I14" s="99"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="108" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="91" t="s">
+      <c r="C15" s="83"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="108" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="83"/>
+      <c r="F15" s="80"/>
       <c r="G15" t="s">
         <v>139</v>
       </c>
@@ -3311,15 +3311,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="91" t="s">
+      <c r="B16" s="108" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="91" t="s">
+      <c r="C16" s="83"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="83"/>
+      <c r="F16" s="80"/>
       <c r="G16" t="s">
         <v>139</v>
       </c>
@@ -3330,15 +3330,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="108" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91" t="s">
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="91"/>
+      <c r="F17" s="108"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -3349,15 +3349,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="91" t="s">
+      <c r="B18" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="91" t="s">
+      <c r="C18" s="83"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="83"/>
+      <c r="F18" s="80"/>
       <c r="G18" t="s">
         <v>139</v>
       </c>
@@ -3366,11 +3366,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="82"/>
+      <c r="B19" s="109"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -3401,46 +3401,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -3455,6 +3455,30 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="B9:I9"/>
@@ -3469,30 +3493,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -3520,14 +3520,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -3540,19 +3540,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3571,10 +3571,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3594,10 +3594,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3619,140 +3619,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75" t="s">
+      <c r="F13" s="72"/>
+      <c r="G13" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="72"/>
+      <c r="I13" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="75"/>
+      <c r="I14" s="72"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -3796,15 +3796,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80" t="s">
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="80"/>
+      <c r="F17" s="86"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -3813,22 +3813,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -3859,46 +3859,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -3913,6 +3913,32 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -3925,32 +3951,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -3978,14 +3978,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -3998,19 +3998,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4029,10 +4029,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4052,10 +4052,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4077,140 +4077,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75" t="s">
+      <c r="F13" s="72"/>
+      <c r="G13" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="72"/>
+      <c r="I13" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="75"/>
+      <c r="I14" s="72"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -4314,46 +4314,46 @@
       <c r="A21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
       <c r="E21" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
@@ -4368,6 +4368,30 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -4380,30 +4404,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -4430,14 +4430,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -4450,19 +4450,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4481,10 +4481,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4504,10 +4504,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4529,140 +4529,140 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75" t="s">
+      <c r="F13" s="72"/>
+      <c r="G13" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="72"/>
+      <c r="I13" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
       <c r="G14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="75"/>
+      <c r="I14" s="72"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
@@ -4706,15 +4706,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="86" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80" t="s">
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="F17" s="80"/>
+      <c r="F17" s="86"/>
       <c r="G17" t="s">
         <v>139</v>
       </c>
@@ -4725,15 +4725,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80" t="s">
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86" t="s">
         <v>134</v>
       </c>
-      <c r="F18" s="80"/>
+      <c r="F18" s="86"/>
       <c r="G18" t="s">
         <v>139</v>
       </c>
@@ -4742,11 +4742,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -4777,46 +4777,46 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -4831,32 +4831,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B24:D24"/>
@@ -4869,6 +4843,32 @@
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
@@ -4895,14 +4895,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
         <v>141</v>
@@ -4915,19 +4915,19 @@
       <c r="B2" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
@@ -4946,10 +4946,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4969,10 +4969,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4994,198 +4994,198 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="90" t="s">
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="77" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="64"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="64"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="64"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="75" t="s">
+      <c r="A17" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75" t="s">
+      <c r="F17" s="72"/>
+      <c r="G17" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75" t="s">
+      <c r="H17" s="72"/>
+      <c r="I17" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
       <c r="G18" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="75"/>
+      <c r="I18" s="72"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="86" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80" t="s">
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="F19" s="80"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -5194,28 +5194,28 @@
       <c r="A20" s="4">
         <v>2</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="86" t="s">
         <v>148</v>
       </c>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80" t="s">
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="80"/>
+      <c r="F20" s="86"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80" t="s">
+      <c r="B21" s="86"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86" t="s">
         <v>150</v>
       </c>
-      <c r="F21" s="80"/>
+      <c r="F21" s="86"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
@@ -5224,15 +5224,15 @@
       <c r="A22" s="4">
         <v>3</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="86" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80" t="s">
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86" t="s">
         <v>152</v>
       </c>
-      <c r="F22" s="80"/>
+      <c r="F22" s="86"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
@@ -5241,15 +5241,15 @@
       <c r="A23" s="4">
         <v>4</v>
       </c>
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="86" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80" t="s">
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="F23" s="80"/>
+      <c r="F23" s="86"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
@@ -5258,114 +5258,114 @@
       <c r="A24" s="4">
         <v>5</v>
       </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80" t="s">
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="80"/>
+      <c r="F24" s="86"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="80"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="80"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
@@ -5396,46 +5396,46 @@
       <c r="A36" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
       <c r="E36" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="64"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67"/>
-      <c r="D37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="67"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="64"/>
-      <c r="B38" s="67"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="64"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
     </row>
     <row r="40" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58" t="s">
@@ -5450,16 +5450,42 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="B24:D24"/>
@@ -5476,42 +5502,16 @@
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{4C4DB9CF-C79C-4E5A-A850-965613BF762B}"/>
@@ -5537,14 +5537,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
         <v>141</v>
@@ -5557,19 +5557,19 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78" t="s">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -5586,10 +5586,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="79"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5607,10 +5607,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5632,353 +5632,353 @@
       <c r="F5" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="90" t="s">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="88"/>
       <c r="I6" s="55"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="75" t="s">
+      <c r="A17" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75" t="s">
+      <c r="F17" s="72"/>
+      <c r="G17" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75" t="s">
+      <c r="H17" s="72"/>
+      <c r="I17" s="72" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
       <c r="G18" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="75"/>
+      <c r="I18" s="72"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44">
         <v>1</v>
       </c>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
+      <c r="B21" s="86"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="86"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="86"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="86"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="80"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="80"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="44"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="80"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="86"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="44"/>
@@ -6009,46 +6009,46 @@
       <c r="A37" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
       <c r="E37" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="79"/>
+      <c r="I37" s="79"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
-      <c r="B38" s="67"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
     </row>
     <row r="41" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
@@ -6063,12 +6063,52 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="B6:F6"/>
@@ -6081,52 +6121,12 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
